--- a/EC_resources/ITS工作录/南工其境报名表总表.xlsx
+++ b/EC_resources/ITS工作录/南工其境报名表总表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\86189\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\ITS_Log\EC_resources\ITS工作录\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A664ABC5-A179-4C5A-A1FA-56F655CF18A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5F8A89-6DD6-4935-90E6-8D74496DE7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="南工其境报名信息投递" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1249,25 +1252,25 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N138"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.3984375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.73046875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.53125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.46484375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="24.19921875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.59765625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.73046875" customWidth="1"/>
+    <col min="1" max="1" width="5.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="12.3984375" customWidth="1"/>
-    <col min="11" max="11" width="12.1328125" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="13.265625" customWidth="1"/>
-    <col min="14" max="14" width="14.6640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>120</v>
       </c>
@@ -1311,21 +1314,21 @@
         <v>249</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>4</v>
@@ -1339,21 +1342,21 @@
       <c r="M2" s="9"/>
       <c r="N2" s="8"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>4</v>
@@ -1367,21 +1370,21 @@
       <c r="M3" s="9"/>
       <c r="N3" s="8"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>4</v>
@@ -1395,21 +1398,21 @@
       <c r="M4" s="9"/>
       <c r="N4" s="8"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>4</v>
@@ -1423,18 +1426,18 @@
       <c r="M5" s="9"/>
       <c r="N5" s="8"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>13</v>
@@ -1451,18 +1454,18 @@
       <c r="M6" s="9"/>
       <c r="N6" s="8"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>13</v>
@@ -1479,18 +1482,18 @@
       <c r="M7" s="9"/>
       <c r="N7" s="8"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>13</v>
@@ -1507,21 +1510,21 @@
       <c r="M8" s="9"/>
       <c r="N8" s="8"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>4</v>
@@ -1535,21 +1538,21 @@
       <c r="M9" s="9"/>
       <c r="N9" s="8"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>4</v>
@@ -1563,21 +1566,21 @@
       <c r="M10" s="9"/>
       <c r="N10" s="8"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>4</v>
@@ -1591,21 +1594,21 @@
       <c r="M11" s="9"/>
       <c r="N11" s="8"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>4</v>
@@ -1619,18 +1622,18 @@
       <c r="M12" s="9"/>
       <c r="N12" s="8"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>13</v>
@@ -1647,18 +1650,18 @@
       <c r="M13" s="9"/>
       <c r="N13" s="8"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>13</v>
@@ -1675,18 +1678,18 @@
       <c r="M14" s="9"/>
       <c r="N14" s="8"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>13</v>
@@ -1703,18 +1706,18 @@
       <c r="M15" s="9"/>
       <c r="N15" s="8"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>13</v>
@@ -1731,18 +1734,18 @@
       <c r="M16" s="9"/>
       <c r="N16" s="8"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>13</v>
@@ -1759,18 +1762,18 @@
       <c r="M17" s="9"/>
       <c r="N17" s="8"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>13</v>
@@ -1787,18 +1790,18 @@
       <c r="M18" s="9"/>
       <c r="N18" s="8"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>13</v>
@@ -1815,21 +1818,21 @@
       <c r="M19" s="9"/>
       <c r="N19" s="8"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>4</v>
@@ -1843,21 +1846,21 @@
       <c r="M20" s="9"/>
       <c r="N20" s="8"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>42</v>
+        <v>106</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>4</v>
@@ -1871,21 +1874,21 @@
       <c r="M21" s="9"/>
       <c r="N21" s="8"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>4</v>
@@ -1899,21 +1902,21 @@
       <c r="M22" s="9"/>
       <c r="N22" s="8"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
+        <v>54</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>4</v>
@@ -1927,108 +1930,112 @@
       <c r="M23" s="9"/>
       <c r="N23" s="8"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A24" s="2">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
+        <f>A23+1</f>
+        <v>55</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
       <c r="M24" s="9"/>
       <c r="N24" s="8"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A25" s="2">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <f>A24+1</f>
+        <v>56</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
       <c r="M25" s="9"/>
       <c r="N25" s="8"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A26" s="2">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
+        <f>A25+1</f>
+        <v>57</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
       <c r="M26" s="9"/>
       <c r="N26" s="8"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A27" s="2">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>4</v>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <f>A26+1</f>
+        <v>58</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="3"/>
@@ -2039,24 +2046,25 @@
       <c r="M27" s="9"/>
       <c r="N27" s="8"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A28" s="2">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>4</v>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <f>A27+1</f>
+        <v>59</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="3"/>
@@ -2067,24 +2075,25 @@
       <c r="M28" s="9"/>
       <c r="N28" s="8"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A29" s="2">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>4</v>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <f>A28+1</f>
+        <v>60</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="3"/>
@@ -2095,24 +2104,25 @@
       <c r="M29" s="9"/>
       <c r="N29" s="8"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A30" s="2">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="2" t="s">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <f>A29+1</f>
+        <v>61</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>4</v>
+      <c r="D30" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="3"/>
@@ -2123,24 +2133,25 @@
       <c r="M30" s="9"/>
       <c r="N30" s="8"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A31" s="2">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2" t="s">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <f>A30+1</f>
         <v>62</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>4</v>
+      <c r="B31" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="3"/>
@@ -2151,24 +2162,25 @@
       <c r="M31" s="9"/>
       <c r="N31" s="8"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A32" s="2">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="2" t="s">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <f>A31+1</f>
+        <v>63</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>4</v>
+      <c r="D32" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="3"/>
@@ -2179,24 +2191,25 @@
       <c r="M32" s="9"/>
       <c r="N32" s="8"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A33" s="2">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>4</v>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <f>A32+1</f>
+        <v>64</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="3"/>
@@ -2207,24 +2220,25 @@
       <c r="M33" s="9"/>
       <c r="N33" s="8"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A34" s="2">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E34" s="2" t="s">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <f>A33+1</f>
+        <v>65</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>4</v>
+      <c r="F34" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="3"/>
@@ -2235,553 +2249,572 @@
       <c r="M34" s="9"/>
       <c r="N34" s="8"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A35" s="2">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G35" s="2"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <f>A34+1</f>
+        <v>66</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="G35" s="8"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
       <c r="M35" s="9"/>
       <c r="N35" s="8"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A36" s="2">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E36" s="2" t="s">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <f>A35+1</f>
+        <v>67</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C36" s="5">
+        <v>2023</v>
+      </c>
+      <c r="D36" s="5">
+        <v>2023313513</v>
+      </c>
+      <c r="E36" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F36" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G36" s="2"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
+      <c r="F36" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G36" s="8"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
       <c r="M36" s="9"/>
       <c r="N36" s="8"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A37" s="2">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E37" s="2" t="s">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <f>A36+1</f>
+        <v>68</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C37" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D37" s="5">
+        <v>2025311081</v>
+      </c>
+      <c r="E37" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
+      <c r="F37" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G37" s="8"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
       <c r="M37" s="9"/>
       <c r="N37" s="8"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A38" s="2">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G38" s="2"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
+        <f>A37+1</f>
+        <v>69</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C38" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D38" s="5">
+        <v>2025310874</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G38" s="8"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
       <c r="M38" s="9"/>
       <c r="N38" s="8"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A39" s="2">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G39" s="2"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
+        <f>A38+1</f>
+        <v>70</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C39" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D39" s="5">
+        <v>2025310248</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G39" s="8"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
       <c r="M39" s="9"/>
       <c r="N39" s="8"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A40" s="2">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G40" s="2"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
+        <f>A39+1</f>
+        <v>71</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C40" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D40" s="5">
+        <v>2025311630</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G40" s="8"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
       <c r="M40" s="9"/>
       <c r="N40" s="8"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A41" s="2">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E41" s="2" t="s">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <f>A40+1</f>
+        <v>72</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C41" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D41" s="5">
+        <v>2025310500</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F41" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G41" s="2"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
+      <c r="F41" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G41" s="8"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
       <c r="M41" s="9"/>
       <c r="N41" s="8"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A42" s="2">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E42" s="2" t="s">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <f>A41+1</f>
+        <v>73</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C42" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D42" s="5">
+        <v>2025310921</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G42" s="2"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
+      <c r="F42" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="7"/>
       <c r="M42" s="9"/>
       <c r="N42" s="8"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A43" s="2">
-        <v>42</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="2"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
+        <f>A42+1</f>
+        <v>74</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C43" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D43" s="5">
+        <v>2025310474</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7"/>
       <c r="M43" s="9"/>
       <c r="N43" s="8"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A44" s="2">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="2"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
+        <f>A43+1</f>
+        <v>75</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C44" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D44" s="5">
+        <v>2025311534</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7"/>
       <c r="M44" s="9"/>
       <c r="N44" s="8"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A45" s="2">
-        <v>44</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G45" s="2"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3"/>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <f>A44+1</f>
+        <v>76</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C45" s="5">
+        <v>2024</v>
+      </c>
+      <c r="D45" s="5">
+        <v>2024312094</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="7"/>
       <c r="M45" s="9"/>
       <c r="N45" s="8"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A46" s="2">
-        <v>45</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
+        <f>A45+1</f>
+        <v>77</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C46" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D46" s="5">
+        <v>2025311258</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
       <c r="M46" s="9"/>
       <c r="N46" s="8"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A47" s="2">
-        <v>46</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <f>A46+1</f>
+        <v>78</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C47" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D47" s="5">
+        <v>2025310023</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
       <c r="M47" s="9"/>
       <c r="N47" s="8"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A48" s="2">
-        <v>47</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E48" s="2" t="s">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
+        <f>A47+1</f>
+        <v>79</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C48" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D48" s="5">
+        <v>2025311587</v>
+      </c>
+      <c r="E48" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F48" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G48" s="2"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
+      <c r="F48" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
       <c r="M48" s="9"/>
       <c r="N48" s="8"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A49" s="2">
-        <v>48</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G49" s="2"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
+        <f>A48+1</f>
+        <v>80</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C49" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D49" s="5">
+        <v>2025311506</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
       <c r="M49" s="9"/>
       <c r="N49" s="8"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A50" s="2">
-        <v>49</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E50" s="2" t="s">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="5">
+        <f>A49+1</f>
+        <v>81</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C50" s="5">
+        <v>2024</v>
+      </c>
+      <c r="D50" s="5">
+        <v>2024312906</v>
+      </c>
+      <c r="E50" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G50" s="2"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
+      <c r="F50" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
       <c r="M50" s="9"/>
       <c r="N50" s="8"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A51" s="2">
-        <v>50</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E51" s="2" t="s">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
+        <f>A50+1</f>
+        <v>82</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C51" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D51" s="5">
+        <v>2025310876</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F51" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G51" s="2"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
+      <c r="F51" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7"/>
+      <c r="L51" s="7"/>
       <c r="M51" s="9"/>
       <c r="N51" s="8"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A52" s="2">
-        <v>51</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E52" s="2" t="s">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" s="5">
+        <f>A51+1</f>
+        <v>83</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C52" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D52" s="5">
+        <v>2025311021</v>
+      </c>
+      <c r="E52" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F52" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="2"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3"/>
+      <c r="F52" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="7"/>
+      <c r="J52" s="7"/>
+      <c r="K52" s="7"/>
+      <c r="L52" s="7"/>
       <c r="M52" s="9"/>
       <c r="N52" s="8"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A53" s="2">
-        <v>52</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E53" s="2" t="s">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" s="5">
+        <f>A52+1</f>
+        <v>84</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C53" s="5">
+        <v>2025</v>
+      </c>
+      <c r="D53" s="5">
+        <v>2025310378</v>
+      </c>
+      <c r="E53" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G53" s="2"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="3"/>
+      <c r="F53" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
       <c r="M53" s="9"/>
       <c r="N53" s="8"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>109</v>
+        <v>2</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>4</v>
@@ -2795,21 +2828,21 @@
       <c r="M54" s="9"/>
       <c r="N54" s="8"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>110</v>
+        <v>5</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>111</v>
+        <v>6</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>4</v>
@@ -2823,18 +2856,18 @@
       <c r="M55" s="9"/>
       <c r="N55" s="8"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>112</v>
+        <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>113</v>
+        <v>8</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>3</v>
@@ -2851,18 +2884,18 @@
       <c r="M56" s="9"/>
       <c r="N56" s="8"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>114</v>
+        <v>9</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>115</v>
+        <v>10</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>3</v>
@@ -2879,18 +2912,18 @@
       <c r="M57" s="9"/>
       <c r="N57" s="8"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>3</v>
@@ -2907,18 +2940,18 @@
       <c r="M58" s="9"/>
       <c r="N58" s="8"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>3</v>
@@ -2935,460 +2968,444 @@
       <c r="M59" s="9"/>
       <c r="N59" s="8"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A60" s="5">
-        <f>A59+1</f>
-        <v>59</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
-      <c r="I60" s="7"/>
-      <c r="J60" s="7"/>
-      <c r="K60" s="7"/>
-      <c r="L60" s="7"/>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>10</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G60" s="2"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3"/>
       <c r="M60" s="9"/>
       <c r="N60" s="8"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A61" s="5">
-        <f t="shared" ref="A61:A124" si="0">A60+1</f>
-        <v>60</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
-      <c r="I61" s="7"/>
-      <c r="J61" s="7"/>
-      <c r="K61" s="7"/>
-      <c r="L61" s="7"/>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>11</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G61" s="2"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
       <c r="M61" s="9"/>
       <c r="N61" s="8"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A62" s="5">
-        <f t="shared" si="0"/>
-        <v>61</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="7"/>
-      <c r="K62" s="7"/>
-      <c r="L62" s="7"/>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>19</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="2"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3"/>
       <c r="M62" s="9"/>
       <c r="N62" s="8"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A63" s="5">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G63" s="7"/>
-      <c r="H63" s="7"/>
-      <c r="I63" s="7"/>
-      <c r="J63" s="7"/>
-      <c r="K63" s="7"/>
-      <c r="L63" s="7"/>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>20</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G63" s="2"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="3"/>
+      <c r="L63" s="3"/>
       <c r="M63" s="9"/>
       <c r="N63" s="8"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A64" s="5">
-        <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C64" s="5" t="s">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>21</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D64" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G64" s="7"/>
-      <c r="H64" s="7"/>
-      <c r="I64" s="7"/>
-      <c r="J64" s="7"/>
-      <c r="K64" s="7"/>
-      <c r="L64" s="7"/>
+      <c r="D64" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G64" s="2"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3"/>
       <c r="M64" s="9"/>
       <c r="N64" s="8"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A65" s="5">
-        <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C65" s="5" t="s">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>22</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D65" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G65" s="7"/>
-      <c r="H65" s="7"/>
-      <c r="I65" s="7"/>
-      <c r="J65" s="7"/>
-      <c r="K65" s="7"/>
-      <c r="L65" s="7"/>
+      <c r="D65" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G65" s="2"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3"/>
+      <c r="L65" s="3"/>
       <c r="M65" s="9"/>
       <c r="N65" s="8"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A66" s="5">
-        <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G66" s="7"/>
-      <c r="H66" s="7"/>
-      <c r="I66" s="7"/>
-      <c r="J66" s="7"/>
-      <c r="K66" s="7"/>
-      <c r="L66" s="7"/>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>23</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G66" s="2"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3"/>
       <c r="M66" s="9"/>
       <c r="N66" s="8"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A67" s="5">
-        <f t="shared" si="0"/>
-        <v>66</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G67" s="7"/>
-      <c r="H67" s="7"/>
-      <c r="I67" s="7"/>
-      <c r="J67" s="7"/>
-      <c r="K67" s="7"/>
-      <c r="L67" s="7"/>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>24</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G67" s="2"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3"/>
       <c r="M67" s="9"/>
       <c r="N67" s="8"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A68" s="5">
-        <f t="shared" si="0"/>
-        <v>67</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="7"/>
-      <c r="J68" s="7"/>
-      <c r="K68" s="7"/>
-      <c r="L68" s="7"/>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>25</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G68" s="2"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3"/>
       <c r="M68" s="9"/>
       <c r="N68" s="8"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A69" s="5">
-        <f t="shared" si="0"/>
-        <v>68</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
-      <c r="I69" s="7"/>
-      <c r="J69" s="7"/>
-      <c r="K69" s="7"/>
-      <c r="L69" s="7"/>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>26</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G69" s="2"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3"/>
       <c r="M69" s="9"/>
       <c r="N69" s="8"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A70" s="5">
-        <f t="shared" si="0"/>
-        <v>69</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
-      <c r="I70" s="7"/>
-      <c r="J70" s="7"/>
-      <c r="K70" s="7"/>
-      <c r="L70" s="7"/>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>27</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G70" s="2"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3"/>
+      <c r="K70" s="3"/>
+      <c r="L70" s="3"/>
       <c r="M70" s="9"/>
       <c r="N70" s="8"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A71" s="5">
-        <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G71" s="7"/>
-      <c r="H71" s="7"/>
-      <c r="I71" s="7"/>
-      <c r="J71" s="7"/>
-      <c r="K71" s="7"/>
-      <c r="L71" s="7"/>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>28</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G71" s="2"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="3"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3"/>
+      <c r="L71" s="3"/>
       <c r="M71" s="9"/>
       <c r="N71" s="8"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A72" s="5">
-        <f t="shared" si="0"/>
-        <v>71</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C72" s="5" t="s">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>29</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D72" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G72" s="7"/>
-      <c r="H72" s="7"/>
-      <c r="I72" s="7"/>
-      <c r="J72" s="7"/>
-      <c r="K72" s="7"/>
-      <c r="L72" s="7"/>
+      <c r="D72" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G72" s="2"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3"/>
       <c r="M72" s="9"/>
       <c r="N72" s="8"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A73" s="5">
-        <f t="shared" si="0"/>
-        <v>72</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G73" s="7"/>
-      <c r="H73" s="7"/>
-      <c r="I73" s="7"/>
-      <c r="J73" s="7"/>
-      <c r="K73" s="7"/>
-      <c r="L73" s="7"/>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>30</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G73" s="2"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3"/>
+      <c r="L73" s="3"/>
       <c r="M73" s="9"/>
       <c r="N73" s="8"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A74" s="5">
-        <f t="shared" si="0"/>
-        <v>73</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
-      <c r="L74" s="7"/>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>31</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G74" s="2"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3"/>
+      <c r="L74" s="3"/>
       <c r="M74" s="9"/>
       <c r="N74" s="8"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A75" s="5">
-        <f t="shared" si="0"/>
-        <v>74</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>161</v>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>32</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="3"/>
@@ -3399,25 +3416,24 @@
       <c r="M75" s="9"/>
       <c r="N75" s="8"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A76" s="5">
-        <f t="shared" si="0"/>
-        <v>75</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>161</v>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>34</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="3"/>
@@ -3428,25 +3444,24 @@
       <c r="M76" s="9"/>
       <c r="N76" s="8"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A77" s="5">
-        <f t="shared" si="0"/>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>37</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B77" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="C77" s="5" t="s">
+      <c r="C77" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D77" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>161</v>
+      <c r="D77" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="3"/>
@@ -3457,25 +3472,24 @@
       <c r="M77" s="9"/>
       <c r="N77" s="8"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A78" s="5">
-        <f t="shared" si="0"/>
-        <v>77</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>161</v>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>38</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="3"/>
@@ -3486,25 +3500,24 @@
       <c r="M78" s="9"/>
       <c r="N78" s="8"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A79" s="5">
-        <f t="shared" si="0"/>
-        <v>78</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>161</v>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>39</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="3"/>
@@ -3515,25 +3528,24 @@
       <c r="M79" s="9"/>
       <c r="N79" s="8"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A80" s="5">
-        <f t="shared" si="0"/>
-        <v>79</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C80" s="5" t="s">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>42</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D80" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>161</v>
+      <c r="D80" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="3"/>
@@ -3544,25 +3556,24 @@
       <c r="M80" s="9"/>
       <c r="N80" s="8"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A81" s="5">
-        <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>161</v>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>43</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="3"/>
@@ -3573,25 +3584,24 @@
       <c r="M81" s="9"/>
       <c r="N81" s="8"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A82" s="5">
-        <f t="shared" si="0"/>
-        <v>81</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="C82" s="5" t="s">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>44</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D82" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>161</v>
+      <c r="D82" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="G82" s="2"/>
       <c r="H82" s="3"/>
@@ -3602,25 +3612,24 @@
       <c r="M82" s="9"/>
       <c r="N82" s="8"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A83" s="5">
-        <f t="shared" si="0"/>
-        <v>82</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="C83" s="5" t="s">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
+        <v>45</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D83" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>161</v>
+      <c r="D83" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="3"/>
@@ -3631,25 +3640,24 @@
       <c r="M83" s="9"/>
       <c r="N83" s="8"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A84" s="5">
-        <f t="shared" si="0"/>
-        <v>83</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>161</v>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>46</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="3"/>
@@ -3660,25 +3668,24 @@
       <c r="M84" s="9"/>
       <c r="N84" s="8"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A85" s="5">
-        <f t="shared" si="0"/>
-        <v>84</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>161</v>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A85" s="2">
+        <v>48</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="3"/>
@@ -3689,25 +3696,24 @@
       <c r="M85" s="9"/>
       <c r="N85" s="8"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A86" s="5">
-        <f t="shared" si="0"/>
-        <v>85</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>161</v>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <v>55</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="3"/>
@@ -3718,25 +3724,24 @@
       <c r="M86" s="9"/>
       <c r="N86" s="8"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A87" s="5">
-        <f t="shared" si="0"/>
-        <v>86</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>161</v>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
+        <v>56</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="3"/>
@@ -3747,25 +3752,24 @@
       <c r="M87" s="9"/>
       <c r="N87" s="8"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A88" s="5">
-        <f t="shared" si="0"/>
-        <v>87</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>161</v>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>57</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="3"/>
@@ -3776,25 +3780,24 @@
       <c r="M88" s="9"/>
       <c r="N88" s="8"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A89" s="5">
-        <f t="shared" si="0"/>
-        <v>88</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>161</v>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A89" s="2">
+        <v>58</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="3"/>
@@ -3805,19 +3808,19 @@
       <c r="M89" s="9"/>
       <c r="N89" s="8"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
-        <f t="shared" si="0"/>
-        <v>89</v>
+        <f>A89+1</f>
+        <v>59</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>216</v>
+        <v>159</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>217</v>
+        <v>160</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>3</v>
@@ -3825,57 +3828,57 @@
       <c r="F90" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G90" s="2"/>
-      <c r="H90" s="3"/>
-      <c r="I90" s="3"/>
-      <c r="J90" s="3"/>
-      <c r="K90" s="3"/>
-      <c r="L90" s="3"/>
+      <c r="G90" s="7"/>
+      <c r="H90" s="7"/>
+      <c r="I90" s="7"/>
+      <c r="J90" s="7"/>
+      <c r="K90" s="7"/>
+      <c r="L90" s="7"/>
       <c r="M90" s="9"/>
       <c r="N90" s="8"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
-        <f t="shared" si="0"/>
-        <v>90</v>
+        <f>A90+1</f>
+        <v>60</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>218</v>
+        <v>162</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>219</v>
+        <v>163</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G91" s="2"/>
-      <c r="H91" s="3"/>
-      <c r="I91" s="3"/>
-      <c r="J91" s="3"/>
-      <c r="K91" s="3"/>
-      <c r="L91" s="3"/>
+      <c r="G91" s="7"/>
+      <c r="H91" s="7"/>
+      <c r="I91" s="7"/>
+      <c r="J91" s="7"/>
+      <c r="K91" s="7"/>
+      <c r="L91" s="7"/>
       <c r="M91" s="9"/>
       <c r="N91" s="8"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
-        <f t="shared" si="0"/>
-        <v>91</v>
+        <f>A91+1</f>
+        <v>61</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>220</v>
+        <v>164</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>221</v>
+        <v>165</v>
       </c>
       <c r="E92" s="5" t="s">
         <v>3</v>
@@ -3883,28 +3886,28 @@
       <c r="F92" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G92" s="2"/>
-      <c r="H92" s="3"/>
-      <c r="I92" s="3"/>
-      <c r="J92" s="3"/>
-      <c r="K92" s="3"/>
-      <c r="L92" s="3"/>
+      <c r="G92" s="7"/>
+      <c r="H92" s="7"/>
+      <c r="I92" s="7"/>
+      <c r="J92" s="7"/>
+      <c r="K92" s="7"/>
+      <c r="L92" s="7"/>
       <c r="M92" s="9"/>
       <c r="N92" s="8"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
-        <f t="shared" si="0"/>
-        <v>92</v>
+        <f>A92+1</f>
+        <v>62</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>222</v>
+        <v>169</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>223</v>
+        <v>170</v>
       </c>
       <c r="E93" s="5" t="s">
         <v>3</v>
@@ -3912,57 +3915,57 @@
       <c r="F93" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G93" s="2"/>
-      <c r="H93" s="3"/>
-      <c r="I93" s="3"/>
-      <c r="J93" s="3"/>
-      <c r="K93" s="3"/>
-      <c r="L93" s="3"/>
+      <c r="G93" s="7"/>
+      <c r="H93" s="7"/>
+      <c r="I93" s="7"/>
+      <c r="J93" s="7"/>
+      <c r="K93" s="7"/>
+      <c r="L93" s="7"/>
       <c r="M93" s="9"/>
       <c r="N93" s="8"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
-        <f t="shared" si="0"/>
-        <v>93</v>
+        <f>A93+1</f>
+        <v>63</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G94" s="2"/>
-      <c r="H94" s="3"/>
-      <c r="I94" s="3"/>
-      <c r="J94" s="3"/>
-      <c r="K94" s="3"/>
-      <c r="L94" s="3"/>
+      <c r="G94" s="7"/>
+      <c r="H94" s="7"/>
+      <c r="I94" s="7"/>
+      <c r="J94" s="7"/>
+      <c r="K94" s="7"/>
+      <c r="L94" s="7"/>
       <c r="M94" s="9"/>
       <c r="N94" s="8"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
-        <f t="shared" si="0"/>
-        <v>94</v>
+        <f>A94+1</f>
+        <v>64</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>224</v>
+        <v>175</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
       <c r="E95" s="5" t="s">
         <v>3</v>
@@ -3970,28 +3973,28 @@
       <c r="F95" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G95" s="2"/>
-      <c r="H95" s="3"/>
-      <c r="I95" s="3"/>
-      <c r="J95" s="3"/>
-      <c r="K95" s="3"/>
-      <c r="L95" s="3"/>
+      <c r="G95" s="7"/>
+      <c r="H95" s="7"/>
+      <c r="I95" s="7"/>
+      <c r="J95" s="7"/>
+      <c r="K95" s="7"/>
+      <c r="L95" s="7"/>
       <c r="M95" s="9"/>
       <c r="N95" s="8"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
-        <f t="shared" si="0"/>
-        <v>95</v>
+        <f>A95+1</f>
+        <v>65</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>226</v>
+        <v>139</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
       <c r="E96" s="5" t="s">
         <v>3</v>
@@ -3999,28 +4002,28 @@
       <c r="F96" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G96" s="8"/>
-      <c r="H96" s="9"/>
-      <c r="I96" s="9"/>
-      <c r="J96" s="9"/>
-      <c r="K96" s="9"/>
-      <c r="L96" s="9"/>
+      <c r="G96" s="7"/>
+      <c r="H96" s="7"/>
+      <c r="I96" s="7"/>
+      <c r="J96" s="7"/>
+      <c r="K96" s="7"/>
+      <c r="L96" s="7"/>
       <c r="M96" s="9"/>
       <c r="N96" s="8"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
-        <f t="shared" si="0"/>
-        <v>96</v>
+        <f>A96+1</f>
+        <v>66</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>228</v>
+        <v>178</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>229</v>
+        <v>179</v>
       </c>
       <c r="E97" s="5" t="s">
         <v>3</v>
@@ -4028,28 +4031,28 @@
       <c r="F97" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G97" s="8"/>
-      <c r="H97" s="9"/>
-      <c r="I97" s="9"/>
-      <c r="J97" s="9"/>
-      <c r="K97" s="9"/>
-      <c r="L97" s="9"/>
+      <c r="G97" s="7"/>
+      <c r="H97" s="7"/>
+      <c r="I97" s="7"/>
+      <c r="J97" s="7"/>
+      <c r="K97" s="7"/>
+      <c r="L97" s="7"/>
       <c r="M97" s="9"/>
       <c r="N97" s="8"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
-        <f t="shared" si="0"/>
-        <v>97</v>
+        <f>A97+1</f>
+        <v>67</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>54</v>
+        <v>180</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>55</v>
+        <v>181</v>
       </c>
       <c r="E98" s="5" t="s">
         <v>3</v>
@@ -4057,57 +4060,57 @@
       <c r="F98" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G98" s="8"/>
-      <c r="H98" s="9"/>
-      <c r="I98" s="9"/>
-      <c r="J98" s="9"/>
-      <c r="K98" s="9"/>
-      <c r="L98" s="9"/>
+      <c r="G98" s="7"/>
+      <c r="H98" s="7"/>
+      <c r="I98" s="7"/>
+      <c r="J98" s="7"/>
+      <c r="K98" s="7"/>
+      <c r="L98" s="7"/>
       <c r="M98" s="9"/>
       <c r="N98" s="8"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
-        <f t="shared" si="0"/>
-        <v>98</v>
+        <f>A98+1</f>
+        <v>68</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>228</v>
+        <v>182</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>229</v>
+        <v>183</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F99" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G99" s="8"/>
-      <c r="H99" s="9"/>
-      <c r="I99" s="9"/>
-      <c r="J99" s="9"/>
-      <c r="K99" s="9"/>
-      <c r="L99" s="9"/>
+      <c r="G99" s="7"/>
+      <c r="H99" s="7"/>
+      <c r="I99" s="7"/>
+      <c r="J99" s="7"/>
+      <c r="K99" s="7"/>
+      <c r="L99" s="7"/>
       <c r="M99" s="9"/>
       <c r="N99" s="8"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
-        <f t="shared" si="0"/>
-        <v>99</v>
+        <f>A99+1</f>
+        <v>69</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>230</v>
+        <v>184</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>231</v>
+        <v>185</v>
       </c>
       <c r="E100" s="5" t="s">
         <v>3</v>
@@ -4115,28 +4118,28 @@
       <c r="F100" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G100" s="8"/>
-      <c r="H100" s="9"/>
-      <c r="I100" s="9"/>
-      <c r="J100" s="9"/>
-      <c r="K100" s="9"/>
-      <c r="L100" s="9"/>
+      <c r="G100" s="7"/>
+      <c r="H100" s="7"/>
+      <c r="I100" s="7"/>
+      <c r="J100" s="7"/>
+      <c r="K100" s="7"/>
+      <c r="L100" s="7"/>
       <c r="M100" s="9"/>
       <c r="N100" s="8"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <f>A100+1</f>
+        <v>70</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>233</v>
+        <v>187</v>
       </c>
       <c r="E101" s="5" t="s">
         <v>3</v>
@@ -4144,28 +4147,28 @@
       <c r="F101" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G101" s="8"/>
-      <c r="H101" s="9"/>
-      <c r="I101" s="9"/>
-      <c r="J101" s="9"/>
-      <c r="K101" s="9"/>
-      <c r="L101" s="9"/>
+      <c r="G101" s="7"/>
+      <c r="H101" s="7"/>
+      <c r="I101" s="7"/>
+      <c r="J101" s="7"/>
+      <c r="K101" s="7"/>
+      <c r="L101" s="7"/>
       <c r="M101" s="9"/>
       <c r="N101" s="8"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
-        <f t="shared" si="0"/>
-        <v>101</v>
+        <f>A101+1</f>
+        <v>71</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>234</v>
+        <v>188</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>235</v>
+        <v>189</v>
       </c>
       <c r="E102" s="5" t="s">
         <v>3</v>
@@ -4173,28 +4176,28 @@
       <c r="F102" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G102" s="8"/>
-      <c r="H102" s="9"/>
-      <c r="I102" s="9"/>
-      <c r="J102" s="9"/>
-      <c r="K102" s="9"/>
-      <c r="L102" s="9"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3"/>
+      <c r="J102" s="3"/>
+      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
       <c r="M102" s="9"/>
       <c r="N102" s="8"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
-        <f t="shared" si="0"/>
-        <v>102</v>
+        <f>A102+1</f>
+        <v>72</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>237</v>
+        <v>195</v>
       </c>
       <c r="E103" s="5" t="s">
         <v>3</v>
@@ -4202,28 +4205,28 @@
       <c r="F103" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G103" s="8"/>
-      <c r="H103" s="9"/>
-      <c r="I103" s="9"/>
-      <c r="J103" s="9"/>
-      <c r="K103" s="9"/>
-      <c r="L103" s="9"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="3"/>
+      <c r="J103" s="3"/>
+      <c r="K103" s="3"/>
+      <c r="L103" s="3"/>
       <c r="M103" s="9"/>
       <c r="N103" s="8"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
-        <f t="shared" si="0"/>
-        <v>103</v>
+        <f>A103+1</f>
+        <v>73</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>3</v>
@@ -4231,28 +4234,28 @@
       <c r="F104" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G104" s="8"/>
-      <c r="H104" s="9"/>
-      <c r="I104" s="9"/>
-      <c r="J104" s="9"/>
-      <c r="K104" s="9"/>
-      <c r="L104" s="9"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="3"/>
+      <c r="J104" s="3"/>
+      <c r="K104" s="3"/>
+      <c r="L104" s="3"/>
       <c r="M104" s="9"/>
       <c r="N104" s="8"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
-        <f t="shared" si="0"/>
-        <v>104</v>
+        <f>A104+1</f>
+        <v>74</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="E105" s="5" t="s">
         <v>3</v>
@@ -4260,295 +4263,295 @@
       <c r="F105" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G105" s="8"/>
-      <c r="H105" s="9"/>
-      <c r="I105" s="9"/>
-      <c r="J105" s="9"/>
-      <c r="K105" s="9"/>
-      <c r="L105" s="9"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="3"/>
+      <c r="I105" s="3"/>
+      <c r="J105" s="3"/>
+      <c r="K105" s="3"/>
+      <c r="L105" s="3"/>
       <c r="M105" s="9"/>
       <c r="N105" s="8"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
-        <f t="shared" si="0"/>
-        <v>105</v>
+        <f>A105+1</f>
+        <v>75</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C106" s="5">
-        <v>2023</v>
-      </c>
-      <c r="D106" s="5">
-        <v>2023313513</v>
+        <v>178</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>179</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="G106" s="8"/>
-      <c r="H106" s="9"/>
-      <c r="I106" s="9"/>
-      <c r="J106" s="9"/>
-      <c r="K106" s="9"/>
-      <c r="L106" s="9"/>
+        <v>161</v>
+      </c>
+      <c r="G106" s="2"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="3"/>
+      <c r="J106" s="3"/>
+      <c r="K106" s="3"/>
+      <c r="L106" s="3"/>
       <c r="M106" s="9"/>
       <c r="N106" s="8"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
-        <f t="shared" si="0"/>
-        <v>106</v>
+        <f>A106+1</f>
+        <v>76</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C107" s="5">
-        <v>2024</v>
-      </c>
-      <c r="D107" s="5">
-        <v>2024312030</v>
+        <v>206</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="E107" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="G107" s="8"/>
-      <c r="H107" s="9"/>
-      <c r="I107" s="9"/>
-      <c r="J107" s="9"/>
-      <c r="K107" s="9"/>
-      <c r="L107" s="9"/>
+        <v>161</v>
+      </c>
+      <c r="G107" s="2"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="3"/>
+      <c r="J107" s="3"/>
+      <c r="K107" s="3"/>
+      <c r="L107" s="3"/>
       <c r="M107" s="9"/>
       <c r="N107" s="8"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
-        <f t="shared" si="0"/>
-        <v>107</v>
+        <f>A107+1</f>
+        <v>77</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C108" s="5">
-        <v>2024</v>
-      </c>
-      <c r="D108" s="5">
-        <v>2024312183</v>
+        <v>208</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="E108" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="G108" s="8"/>
-      <c r="H108" s="9"/>
-      <c r="I108" s="9"/>
-      <c r="J108" s="9"/>
-      <c r="K108" s="9"/>
-      <c r="L108" s="9"/>
+        <v>161</v>
+      </c>
+      <c r="G108" s="2"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="3"/>
+      <c r="J108" s="3"/>
+      <c r="K108" s="3"/>
+      <c r="L108" s="3"/>
       <c r="M108" s="9"/>
       <c r="N108" s="8"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
-        <f t="shared" si="0"/>
-        <v>108</v>
+        <f>A108+1</f>
+        <v>78</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C109" s="5">
-        <v>2025</v>
-      </c>
-      <c r="D109" s="5">
-        <v>2025311081</v>
+        <v>210</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>211</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="G109" s="8"/>
-      <c r="H109" s="9"/>
-      <c r="I109" s="9"/>
-      <c r="J109" s="9"/>
-      <c r="K109" s="9"/>
-      <c r="L109" s="9"/>
+        <v>161</v>
+      </c>
+      <c r="G109" s="2"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="3"/>
+      <c r="J109" s="3"/>
+      <c r="K109" s="3"/>
+      <c r="L109" s="3"/>
       <c r="M109" s="9"/>
       <c r="N109" s="8"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
-        <f t="shared" si="0"/>
-        <v>109</v>
+        <f>A109+1</f>
+        <v>79</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C110" s="5">
-        <v>2024</v>
-      </c>
-      <c r="D110" s="5">
-        <v>2024312180</v>
+        <v>212</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>213</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="G110" s="8"/>
-      <c r="H110" s="9"/>
-      <c r="I110" s="9"/>
-      <c r="J110" s="9"/>
-      <c r="K110" s="9"/>
-      <c r="L110" s="9"/>
+        <v>161</v>
+      </c>
+      <c r="G110" s="2"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="3"/>
+      <c r="J110" s="3"/>
+      <c r="K110" s="3"/>
+      <c r="L110" s="3"/>
       <c r="M110" s="9"/>
       <c r="N110" s="8"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
-        <f t="shared" si="0"/>
-        <v>110</v>
+        <f>A110+1</f>
+        <v>80</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C111" s="5">
-        <v>2025</v>
-      </c>
-      <c r="D111" s="5">
-        <v>2025310874</v>
+        <v>216</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>217</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="G111" s="8"/>
-      <c r="H111" s="9"/>
-      <c r="I111" s="9"/>
-      <c r="J111" s="9"/>
-      <c r="K111" s="9"/>
-      <c r="L111" s="9"/>
+        <v>161</v>
+      </c>
+      <c r="G111" s="2"/>
+      <c r="H111" s="3"/>
+      <c r="I111" s="3"/>
+      <c r="J111" s="3"/>
+      <c r="K111" s="3"/>
+      <c r="L111" s="3"/>
       <c r="M111" s="9"/>
       <c r="N111" s="8"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
-        <f t="shared" si="0"/>
-        <v>111</v>
+        <f>A111+1</f>
+        <v>81</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C112" s="5">
-        <v>2025</v>
-      </c>
-      <c r="D112" s="5">
-        <v>2025310392</v>
+        <v>220</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="E112" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="G112" s="8"/>
-      <c r="H112" s="9"/>
-      <c r="I112" s="9"/>
-      <c r="J112" s="9"/>
-      <c r="K112" s="9"/>
-      <c r="L112" s="9"/>
+        <v>161</v>
+      </c>
+      <c r="G112" s="2"/>
+      <c r="H112" s="3"/>
+      <c r="I112" s="3"/>
+      <c r="J112" s="3"/>
+      <c r="K112" s="3"/>
+      <c r="L112" s="3"/>
       <c r="M112" s="9"/>
       <c r="N112" s="8"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
-        <f t="shared" si="0"/>
-        <v>112</v>
+        <f>A112+1</f>
+        <v>82</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C113" s="5">
-        <v>2024</v>
-      </c>
-      <c r="D113" s="5">
-        <v>2024312313</v>
+        <v>222</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>223</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="G113" s="8"/>
-      <c r="H113" s="9"/>
-      <c r="I113" s="9"/>
-      <c r="J113" s="9"/>
-      <c r="K113" s="9"/>
-      <c r="L113" s="9"/>
+        <v>161</v>
+      </c>
+      <c r="G113" s="2"/>
+      <c r="H113" s="3"/>
+      <c r="I113" s="3"/>
+      <c r="J113" s="3"/>
+      <c r="K113" s="3"/>
+      <c r="L113" s="3"/>
       <c r="M113" s="9"/>
       <c r="N113" s="8"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
-        <f t="shared" si="0"/>
-        <v>113</v>
+        <f>A113+1</f>
+        <v>83</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C114" s="5">
-        <v>2024</v>
-      </c>
-      <c r="D114" s="5">
-        <v>2024312410</v>
+        <v>224</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>225</v>
       </c>
       <c r="E114" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="G114" s="8"/>
-      <c r="H114" s="9"/>
-      <c r="I114" s="9"/>
-      <c r="J114" s="9"/>
-      <c r="K114" s="9"/>
-      <c r="L114" s="9"/>
+        <v>161</v>
+      </c>
+      <c r="G114" s="2"/>
+      <c r="H114" s="3"/>
+      <c r="I114" s="3"/>
+      <c r="J114" s="3"/>
+      <c r="K114" s="3"/>
+      <c r="L114" s="3"/>
       <c r="M114" s="9"/>
       <c r="N114" s="8"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
-        <f t="shared" si="0"/>
-        <v>114</v>
+        <f>A114+1</f>
+        <v>84</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C115" s="5">
-        <v>2025</v>
+        <v>226</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>137</v>
+        <v>227</v>
       </c>
       <c r="E115" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="G115" s="8"/>
       <c r="H115" s="9"/>
@@ -4559,25 +4562,25 @@
       <c r="M115" s="9"/>
       <c r="N115" s="8"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
-        <f t="shared" si="0"/>
-        <v>115</v>
+        <f>A115+1</f>
+        <v>85</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C116" s="5">
-        <v>2025</v>
-      </c>
-      <c r="D116" s="5">
-        <v>2025310876</v>
+        <v>228</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="E116" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="G116" s="8"/>
       <c r="H116" s="9"/>
@@ -4588,25 +4591,25 @@
       <c r="M116" s="9"/>
       <c r="N116" s="8"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
-        <f t="shared" si="0"/>
-        <v>116</v>
+        <f>A116+1</f>
+        <v>86</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C117" s="5">
-        <v>2025</v>
-      </c>
-      <c r="D117" s="5">
-        <v>2025310746</v>
+        <v>54</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="E117" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="G117" s="8"/>
       <c r="H117" s="9"/>
@@ -4617,25 +4620,25 @@
       <c r="M117" s="9"/>
       <c r="N117" s="8"/>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
-        <f t="shared" si="0"/>
-        <v>117</v>
+        <f>A117+1</f>
+        <v>87</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C118" s="5">
-        <v>2024</v>
-      </c>
-      <c r="D118" s="5">
-        <v>2024311473</v>
+        <v>230</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="G118" s="8"/>
       <c r="H118" s="9"/>
@@ -4646,25 +4649,25 @@
       <c r="M118" s="9"/>
       <c r="N118" s="8"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
-        <f t="shared" si="0"/>
-        <v>118</v>
+        <f>A118+1</f>
+        <v>88</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C119" s="5">
-        <v>2025</v>
-      </c>
-      <c r="D119" s="5">
-        <v>2025310248</v>
+        <v>232</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="G119" s="8"/>
       <c r="H119" s="9"/>
@@ -4675,25 +4678,25 @@
       <c r="M119" s="9"/>
       <c r="N119" s="8"/>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
-        <f t="shared" si="0"/>
-        <v>119</v>
+        <f>A119+1</f>
+        <v>89</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C120" s="5">
-        <v>2025</v>
-      </c>
-      <c r="D120" s="5">
-        <v>2025311630</v>
+        <v>234</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="G120" s="8"/>
       <c r="H120" s="9"/>
@@ -4704,25 +4707,25 @@
       <c r="M120" s="9"/>
       <c r="N120" s="8"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
-        <f t="shared" si="0"/>
-        <v>120</v>
+        <f>A120+1</f>
+        <v>90</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C121" s="5">
-        <v>2025</v>
-      </c>
-      <c r="D121" s="5">
-        <v>2025310271</v>
+        <v>236</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="E121" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="G121" s="8"/>
       <c r="H121" s="9"/>
@@ -4733,25 +4736,25 @@
       <c r="M121" s="9"/>
       <c r="N121" s="8"/>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
-        <f t="shared" si="0"/>
-        <v>121</v>
+        <f>A121+1</f>
+        <v>91</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C122" s="5">
-        <v>2025</v>
-      </c>
-      <c r="D122" s="5">
-        <v>2025310500</v>
+        <v>238</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>239</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="G122" s="8"/>
       <c r="H122" s="9"/>
@@ -4762,77 +4765,77 @@
       <c r="M122" s="9"/>
       <c r="N122" s="8"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
-        <f t="shared" si="0"/>
-        <v>122</v>
+        <f>A122+1</f>
+        <v>92</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C123" s="5">
-        <v>2025</v>
-      </c>
-      <c r="D123" s="5">
-        <v>2025310921</v>
+        <v>240</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="G123" s="7"/>
-      <c r="H123" s="7"/>
-      <c r="I123" s="7"/>
-      <c r="J123" s="7"/>
-      <c r="K123" s="7"/>
-      <c r="L123" s="7"/>
+        <v>161</v>
+      </c>
+      <c r="G123" s="8"/>
+      <c r="H123" s="9"/>
+      <c r="I123" s="9"/>
+      <c r="J123" s="9"/>
+      <c r="K123" s="9"/>
+      <c r="L123" s="9"/>
       <c r="M123" s="9"/>
       <c r="N123" s="8"/>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
-        <f t="shared" si="0"/>
-        <v>123</v>
+        <f>A123+1</f>
+        <v>93</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="C124" s="5">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D124" s="5">
-        <v>2025310474</v>
+        <v>2024312030</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G124" s="7"/>
-      <c r="H124" s="7"/>
-      <c r="I124" s="7"/>
-      <c r="J124" s="7"/>
-      <c r="K124" s="7"/>
-      <c r="L124" s="7"/>
+      <c r="G124" s="8"/>
+      <c r="H124" s="9"/>
+      <c r="I124" s="9"/>
+      <c r="J124" s="9"/>
+      <c r="K124" s="9"/>
+      <c r="L124" s="9"/>
       <c r="M124" s="9"/>
       <c r="N124" s="8"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
-        <f t="shared" ref="A125:A137" si="1">A124+1</f>
-        <v>124</v>
+        <f>A124+1</f>
+        <v>94</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="C125" s="5">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D125" s="5">
-        <v>2025310217</v>
+        <v>2024312183</v>
       </c>
       <c r="E125" s="5" t="s">
         <v>3</v>
@@ -4840,144 +4843,144 @@
       <c r="F125" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G125" s="7"/>
-      <c r="H125" s="7"/>
-      <c r="I125" s="7"/>
-      <c r="J125" s="7"/>
-      <c r="K125" s="7"/>
-      <c r="L125" s="7"/>
+      <c r="G125" s="8"/>
+      <c r="H125" s="9"/>
+      <c r="I125" s="9"/>
+      <c r="J125" s="9"/>
+      <c r="K125" s="9"/>
+      <c r="L125" s="9"/>
       <c r="M125" s="9"/>
       <c r="N125" s="8"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
-        <f t="shared" si="1"/>
-        <v>125</v>
+        <f>A125+1</f>
+        <v>95</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="C126" s="5">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D126" s="5">
-        <v>2025311534</v>
+        <v>2024312180</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F126" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G126" s="7"/>
-      <c r="H126" s="7"/>
-      <c r="I126" s="7"/>
-      <c r="J126" s="7"/>
-      <c r="K126" s="7"/>
-      <c r="L126" s="7"/>
+      <c r="G126" s="8"/>
+      <c r="H126" s="9"/>
+      <c r="I126" s="9"/>
+      <c r="J126" s="9"/>
+      <c r="K126" s="9"/>
+      <c r="L126" s="9"/>
       <c r="M126" s="9"/>
       <c r="N126" s="8"/>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
-        <f t="shared" si="1"/>
-        <v>126</v>
+        <f>A126+1</f>
+        <v>96</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="C127" s="5">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D127" s="5">
-        <v>2024312094</v>
+        <v>2025310392</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G127" s="7"/>
-      <c r="H127" s="7"/>
-      <c r="I127" s="7"/>
-      <c r="J127" s="7"/>
-      <c r="K127" s="7"/>
-      <c r="L127" s="7"/>
+      <c r="G127" s="8"/>
+      <c r="H127" s="9"/>
+      <c r="I127" s="9"/>
+      <c r="J127" s="9"/>
+      <c r="K127" s="9"/>
+      <c r="L127" s="9"/>
       <c r="M127" s="9"/>
       <c r="N127" s="8"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
-        <f t="shared" si="1"/>
-        <v>127</v>
+        <f>A127+1</f>
+        <v>97</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="C128" s="5">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D128" s="5">
-        <v>2025311258</v>
+        <v>2024312313</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F128" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G128" s="7"/>
-      <c r="H128" s="7"/>
-      <c r="I128" s="7"/>
-      <c r="J128" s="7"/>
-      <c r="K128" s="7"/>
-      <c r="L128" s="7"/>
+      <c r="G128" s="8"/>
+      <c r="H128" s="9"/>
+      <c r="I128" s="9"/>
+      <c r="J128" s="9"/>
+      <c r="K128" s="9"/>
+      <c r="L128" s="9"/>
       <c r="M128" s="9"/>
       <c r="N128" s="8"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
-        <f t="shared" si="1"/>
-        <v>128</v>
+        <f>A128+1</f>
+        <v>98</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C129" s="5">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D129" s="5">
-        <v>2025310023</v>
+        <v>2024312410</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F129" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G129" s="7"/>
-      <c r="H129" s="7"/>
-      <c r="I129" s="7"/>
-      <c r="J129" s="7"/>
-      <c r="K129" s="7"/>
-      <c r="L129" s="7"/>
+      <c r="G129" s="8"/>
+      <c r="H129" s="9"/>
+      <c r="I129" s="9"/>
+      <c r="J129" s="9"/>
+      <c r="K129" s="9"/>
+      <c r="L129" s="9"/>
       <c r="M129" s="9"/>
       <c r="N129" s="8"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
-        <f t="shared" si="1"/>
-        <v>129</v>
+        <f>A129+1</f>
+        <v>99</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="C130" s="5">
         <v>2025</v>
       </c>
-      <c r="D130" s="5">
-        <v>2025311382</v>
+      <c r="D130" s="5" t="s">
+        <v>137</v>
       </c>
       <c r="E130" s="5" t="s">
         <v>3</v>
@@ -4985,115 +4988,115 @@
       <c r="F130" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G130" s="7"/>
-      <c r="H130" s="7"/>
-      <c r="I130" s="7"/>
-      <c r="J130" s="7"/>
-      <c r="K130" s="7"/>
-      <c r="L130" s="7"/>
+      <c r="G130" s="8"/>
+      <c r="H130" s="9"/>
+      <c r="I130" s="9"/>
+      <c r="J130" s="9"/>
+      <c r="K130" s="9"/>
+      <c r="L130" s="9"/>
       <c r="M130" s="9"/>
       <c r="N130" s="8"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
-        <f t="shared" si="1"/>
-        <v>130</v>
+        <f>A130+1</f>
+        <v>100</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="C131" s="5">
         <v>2025</v>
       </c>
       <c r="D131" s="5">
-        <v>2025311587</v>
+        <v>2025310876</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G131" s="7"/>
-      <c r="H131" s="7"/>
-      <c r="I131" s="7"/>
-      <c r="J131" s="7"/>
-      <c r="K131" s="7"/>
-      <c r="L131" s="7"/>
+      <c r="G131" s="8"/>
+      <c r="H131" s="9"/>
+      <c r="I131" s="9"/>
+      <c r="J131" s="9"/>
+      <c r="K131" s="9"/>
+      <c r="L131" s="9"/>
       <c r="M131" s="9"/>
       <c r="N131" s="8"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
-        <f t="shared" si="1"/>
-        <v>131</v>
+        <f>A131+1</f>
+        <v>101</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="C132" s="5">
         <v>2025</v>
       </c>
       <c r="D132" s="5">
-        <v>2025311506</v>
+        <v>2025310746</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G132" s="7"/>
-      <c r="H132" s="7"/>
-      <c r="I132" s="7"/>
-      <c r="J132" s="7"/>
-      <c r="K132" s="7"/>
-      <c r="L132" s="7"/>
+      <c r="G132" s="8"/>
+      <c r="H132" s="9"/>
+      <c r="I132" s="9"/>
+      <c r="J132" s="9"/>
+      <c r="K132" s="9"/>
+      <c r="L132" s="9"/>
       <c r="M132" s="9"/>
       <c r="N132" s="8"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
-        <f t="shared" si="1"/>
-        <v>132</v>
+        <f>A132+1</f>
+        <v>102</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C133" s="5">
         <v>2024</v>
       </c>
       <c r="D133" s="5">
-        <v>2024312906</v>
+        <v>2024311473</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G133" s="7"/>
-      <c r="H133" s="7"/>
-      <c r="I133" s="7"/>
-      <c r="J133" s="7"/>
-      <c r="K133" s="7"/>
-      <c r="L133" s="7"/>
+      <c r="G133" s="8"/>
+      <c r="H133" s="9"/>
+      <c r="I133" s="9"/>
+      <c r="J133" s="9"/>
+      <c r="K133" s="9"/>
+      <c r="L133" s="9"/>
       <c r="M133" s="9"/>
       <c r="N133" s="8"/>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
-        <f t="shared" si="1"/>
-        <v>133</v>
+        <f>A133+1</f>
+        <v>103</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="C134" s="5">
         <v>2025</v>
       </c>
       <c r="D134" s="5">
-        <v>2025310325</v>
+        <v>2025310271</v>
       </c>
       <c r="E134" s="5" t="s">
         <v>3</v>
@@ -5101,31 +5104,31 @@
       <c r="F134" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G134" s="7"/>
-      <c r="H134" s="7"/>
-      <c r="I134" s="7"/>
-      <c r="J134" s="7"/>
-      <c r="K134" s="7"/>
-      <c r="L134" s="7"/>
+      <c r="G134" s="8"/>
+      <c r="H134" s="9"/>
+      <c r="I134" s="9"/>
+      <c r="J134" s="9"/>
+      <c r="K134" s="9"/>
+      <c r="L134" s="9"/>
       <c r="M134" s="9"/>
       <c r="N134" s="8"/>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
-        <f t="shared" si="1"/>
-        <v>134</v>
+        <f>A134+1</f>
+        <v>104</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C135" s="5">
         <v>2025</v>
       </c>
       <c r="D135" s="5">
-        <v>2025310876</v>
+        <v>2025310217</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F135" s="5" t="s">
         <v>127</v>
@@ -5139,22 +5142,22 @@
       <c r="M135" s="9"/>
       <c r="N135" s="8"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" s="5">
-        <f t="shared" si="1"/>
-        <v>135</v>
+        <f>A135+1</f>
+        <v>105</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C136" s="5">
         <v>2025</v>
       </c>
       <c r="D136" s="5">
-        <v>2025311021</v>
+        <v>2025311382</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>127</v>
@@ -5168,39 +5171,42 @@
       <c r="M136" s="9"/>
       <c r="N136" s="8"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" s="5">
-        <f t="shared" si="1"/>
-        <v>136</v>
+        <f>A136+1</f>
+        <v>106</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C137" s="5">
         <v>2025</v>
       </c>
       <c r="D137" s="5">
-        <v>2025310378</v>
+        <v>2025310325</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G137" s="5"/>
-      <c r="H137" s="5"/>
-      <c r="I137" s="5"/>
-      <c r="J137" s="5"/>
-      <c r="K137" s="6"/>
-      <c r="L137" s="6"/>
+      <c r="G137" s="7"/>
+      <c r="H137" s="7"/>
+      <c r="I137" s="7"/>
+      <c r="J137" s="7"/>
+      <c r="K137" s="7"/>
+      <c r="L137" s="7"/>
       <c r="M137" s="9"/>
       <c r="N137" s="8"/>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" s="10"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N138">
+    <sortCondition ref="E1:E138"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup firstPageNumber="0" fitToWidth="10" orientation="portrait"/>
